--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-nuva.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-nuva.xlsx
@@ -31,13 +31,13 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.3.6.1.4.1.48601.1</t>
+    <t>https://smt.esante.gouv.fr/#terminologie-nuva</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.787</t>
+    <t>1.0.799</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T00:00:00+00:00</t>
+    <t>2024-11-18T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1628</t>
+    <t>1630</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-nuva.xlsx
+++ b/ig/DM-DECEMBRE-2024/CodeSystem-terminologie-nuva.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.799</t>
+    <t>1.0.818</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18T00:00:00+00:00</t>
+    <t>2024-12-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1630</t>
+    <t>1631</t>
   </si>
   <si>
     <t>Code</t>
